--- a/data/reports/report-2026-07-30-v3.xlsx
+++ b/data/reports/report-2026-07-30-v3.xlsx
@@ -769,7 +769,7 @@
         <v>3.44</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>-8405</v>
+        <v>-10723</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-9030</v>
@@ -1517,7 +1517,7 @@
         <v>4.67</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>93758</v>
+        <v>82566</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>56369</v>
@@ -2534,30 +2534,30 @@
         <v>2798</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0</v>
+        <v>0.4567</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>1</v>
+        <v>1.84</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>1.54</v>
+        <v>5.17</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>710696</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0</v>
+        <v>324568</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>262078</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>448618</v>
+        <v>124050</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.6312</v>
-      </c>
-      <c r="L20" s="25" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="L20" s="29" t="n">
         <v>2.71</v>
       </c>
       <c r="M20" s="10" t="n">
@@ -2567,13 +2567,13 @@
         <v>87592</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>214072</v>
+        <v>82566</v>
       </c>
       <c r="P20" s="16" t="n">
         <v>3.44</v>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>57060</v>
+        <v>29080</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>13000</v>
@@ -28168,7 +28168,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>売価 窓内で変動円 ／ 単価原価 2,798円 ／ 原価率(30日) 0.0% ／ 分岐MER 1.00 ／ 目標MER 1.54</t>
+          <t>売価 窓内で変動円 ／ 単価原価 2,798円 ／ 原価率(30日) 45.7% ／ 分岐MER 1.84 ／ 目標MER 5.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="47" t="inlineStr">
+        <is>
+          <t>※ 売価は7/27に5,980→6,980円へ値上げ。販売数は日付に応じた売価で算出（値上げ当日7/27のみ新旧混在を分解: 旧1個+新5個=6個）</t>
         </is>
       </c>
     </row>
@@ -28231,22 +28238,22 @@
         <v>69800</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0</v>
+        <v>27980</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>12740</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>57060</v>
+        <v>29080</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.8175</v>
+        <v>0.4166</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>5.48</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>4.48</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="8">
@@ -28259,22 +28266,22 @@
         <v>158144</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0</v>
+        <v>64354</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>37421</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>120723</v>
+        <v>56369</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.7634</v>
+        <v>0.3564</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>4.23</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>3.23</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="9">
@@ -28287,22 +28294,22 @@
         <v>301664</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0</v>
+        <v>131506</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>87592</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>214072</v>
+        <v>82566</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.7096</v>
+        <v>0.2737</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>3.44</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
@@ -28315,22 +28322,22 @@
         <v>710696</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0</v>
+        <v>324568</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>262078</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>448618</v>
+        <v>124050</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.6312</v>
+        <v>0.1745</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>2.71</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>1.71</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="12">
@@ -28822,18 +28829,22 @@
       <c r="E25" s="21" t="n">
         <v>1196</v>
       </c>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="21" t="n"/>
+      <c r="F25" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>11192</v>
+      </c>
       <c r="H25" s="21" t="n">
         <v>6174</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>16550</v>
+        <v>5358</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>0.7282999999999999</v>
-      </c>
-      <c r="K25" s="25" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="K25" s="29" t="n">
         <v>3.68</v>
       </c>
       <c r="L25" s="23" t="n">
@@ -28863,18 +28874,22 @@
       <c r="E26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="F26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>11192</v>
+      </c>
       <c r="H26" s="10" t="n">
         <v>10961</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>12959</v>
+        <v>1767</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.5417999999999999</v>
-      </c>
-      <c r="K26" s="25" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="K26" s="29" t="n">
         <v>2.18</v>
       </c>
       <c r="L26" s="16" t="n">
@@ -28904,18 +28919,22 @@
       <c r="E27" s="21" t="n">
         <v>1196</v>
       </c>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="21" t="n"/>
+      <c r="F27" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>25182</v>
+      </c>
       <c r="H27" s="21" t="n">
         <v>15002</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>37622</v>
+        <v>12440</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>0.7149</v>
-      </c>
-      <c r="K27" s="25" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="K27" s="29" t="n">
         <v>3.51</v>
       </c>
       <c r="L27" s="23" t="n">
@@ -28945,18 +28964,22 @@
       <c r="E28" s="10" t="n">
         <v>1196</v>
       </c>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>25182</v>
+      </c>
       <c r="H28" s="10" t="n">
         <v>13215</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>39409</v>
+        <v>14227</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>0.7489</v>
-      </c>
-      <c r="K28" s="25" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="K28" s="29" t="n">
         <v>3.98</v>
       </c>
       <c r="L28" s="16" t="n">
@@ -28986,18 +29009,22 @@
       <c r="E29" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="21" t="n"/>
+      <c r="F29" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>8394</v>
+      </c>
       <c r="H29" s="21" t="n">
         <v>14424</v>
       </c>
-      <c r="I29" s="21" t="n">
-        <v>3516</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="K29" s="29" t="n">
+      <c r="I29" s="28" t="n">
+        <v>-4878</v>
+      </c>
+      <c r="J29" s="43" t="n">
+        <v>-0.2719</v>
+      </c>
+      <c r="K29" s="15" t="n">
         <v>1.24</v>
       </c>
       <c r="L29" s="23" t="n">
@@ -29027,18 +29054,22 @@
       <c r="E30" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="10" t="n"/>
+      <c r="F30" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>8394</v>
+      </c>
       <c r="H30" s="10" t="n">
         <v>15104</v>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>2836</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>0.1581</v>
-      </c>
-      <c r="K30" s="29" t="n">
+      <c r="I30" s="26" t="n">
+        <v>-5558</v>
+      </c>
+      <c r="J30" s="48" t="n">
+        <v>-0.3098</v>
+      </c>
+      <c r="K30" s="15" t="n">
         <v>1.19</v>
       </c>
       <c r="L30" s="16" t="n">
@@ -29068,18 +29099,22 @@
       <c r="E31" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="21" t="n"/>
+      <c r="F31" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>11192</v>
+      </c>
       <c r="H31" s="21" t="n">
         <v>15036</v>
       </c>
-      <c r="I31" s="21" t="n">
-        <v>8884</v>
-      </c>
-      <c r="J31" s="22" t="n">
-        <v>0.3714</v>
-      </c>
-      <c r="K31" s="25" t="n">
+      <c r="I31" s="28" t="n">
+        <v>-2308</v>
+      </c>
+      <c r="J31" s="43" t="n">
+        <v>-0.0965</v>
+      </c>
+      <c r="K31" s="15" t="n">
         <v>1.59</v>
       </c>
       <c r="L31" s="23" t="n">
@@ -29109,18 +29144,22 @@
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="10" t="n"/>
+      <c r="F32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>13990</v>
+      </c>
       <c r="H32" s="10" t="n">
         <v>14548</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>15352</v>
+        <v>1362</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>0.5134</v>
-      </c>
-      <c r="K32" s="25" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="K32" s="29" t="n">
         <v>2.06</v>
       </c>
       <c r="L32" s="16" t="n">
@@ -29150,18 +29189,22 @@
       <c r="E33" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="21" t="n"/>
+      <c r="F33" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>11192</v>
+      </c>
       <c r="H33" s="21" t="n">
         <v>13156</v>
       </c>
-      <c r="I33" s="21" t="n">
-        <v>10764</v>
-      </c>
-      <c r="J33" s="22" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K33" s="25" t="n">
+      <c r="I33" s="28" t="n">
+        <v>-428</v>
+      </c>
+      <c r="J33" s="43" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="K33" s="15" t="n">
         <v>1.82</v>
       </c>
       <c r="L33" s="23" t="n">
@@ -29195,18 +29238,22 @@
       <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="F34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>8394</v>
+      </c>
       <c r="H34" s="10" t="n">
         <v>13431</v>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>4509</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="K34" s="29" t="n">
+      <c r="I34" s="26" t="n">
+        <v>-3885</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>-0.2166</v>
+      </c>
+      <c r="K34" s="15" t="n">
         <v>1.34</v>
       </c>
       <c r="L34" s="16" t="n">
@@ -29240,18 +29287,22 @@
       <c r="E35" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="21" t="n"/>
+      <c r="F35" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>16788</v>
+      </c>
       <c r="H35" s="21" t="n">
         <v>16633</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>19247</v>
+        <v>2459</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>0.5364</v>
-      </c>
-      <c r="K35" s="25" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="K35" s="29" t="n">
         <v>2.16</v>
       </c>
       <c r="L35" s="23" t="n">
@@ -29289,18 +29340,22 @@
       <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="F36" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>19586</v>
+      </c>
       <c r="H36" s="10" t="n">
         <v>15448</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>26412</v>
+        <v>6826</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="K36" s="25" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="K36" s="29" t="n">
         <v>2.71</v>
       </c>
       <c r="L36" s="16" t="n">
@@ -29334,18 +29389,22 @@
       <c r="E37" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="20" t="n"/>
-      <c r="G37" s="21" t="n"/>
+      <c r="F37" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>22384</v>
+      </c>
       <c r="H37" s="21" t="n">
         <v>11354</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>36486</v>
+        <v>14102</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>0.7627</v>
-      </c>
-      <c r="K37" s="25" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="K37" s="29" t="n">
         <v>4.21</v>
       </c>
       <c r="L37" s="23" t="n">
@@ -29379,18 +29438,22 @@
       <c r="E38" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="10" t="n"/>
+      <c r="F38" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>8394</v>
+      </c>
       <c r="H38" s="10" t="n">
         <v>11120</v>
       </c>
-      <c r="I38" s="10" t="n">
-        <v>6820</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>0.3802</v>
-      </c>
-      <c r="K38" s="25" t="n">
+      <c r="I38" s="26" t="n">
+        <v>-1574</v>
+      </c>
+      <c r="J38" s="48" t="n">
+        <v>-0.0877</v>
+      </c>
+      <c r="K38" s="15" t="n">
         <v>1.61</v>
       </c>
       <c r="L38" s="16" t="n">
@@ -29424,18 +29487,22 @@
       <c r="E39" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="21" t="n"/>
+      <c r="F39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>13990</v>
+      </c>
       <c r="H39" s="21" t="n">
         <v>11299</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>18601</v>
+        <v>4611</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>0.6221</v>
-      </c>
-      <c r="K39" s="25" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="K39" s="29" t="n">
         <v>2.65</v>
       </c>
       <c r="L39" s="23" t="n">
@@ -29469,18 +29536,22 @@
       <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="10" t="n"/>
+      <c r="F40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>16788</v>
+      </c>
       <c r="H40" s="10" t="n">
         <v>11442</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>24438</v>
+        <v>7650</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>0.6811</v>
-      </c>
-      <c r="K40" s="25" t="n">
+        <v>0.2132</v>
+      </c>
+      <c r="K40" s="29" t="n">
         <v>3.14</v>
       </c>
       <c r="L40" s="16" t="n">
@@ -29514,18 +29585,22 @@
       <c r="E41" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="21" t="n"/>
+      <c r="F41" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>27980</v>
+      </c>
       <c r="H41" s="21" t="n">
         <v>16310</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>43490</v>
+        <v>15510</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>0.7272999999999999</v>
-      </c>
-      <c r="K41" s="25" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="K41" s="29" t="n">
         <v>3.67</v>
       </c>
       <c r="L41" s="23" t="n">
@@ -29559,18 +29634,22 @@
       <c r="E42" s="10" t="n">
         <v>1396</v>
       </c>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="10" t="n"/>
+      <c r="F42" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>16788</v>
+      </c>
       <c r="H42" s="10" t="n">
         <v>13724</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>25760</v>
+        <v>8972</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>0.6524</v>
-      </c>
-      <c r="K42" s="25" t="n">
+        <v>0.2272</v>
+      </c>
+      <c r="K42" s="29" t="n">
         <v>2.88</v>
       </c>
       <c r="L42" s="16" t="n">
@@ -29608,18 +29687,22 @@
       <c r="E43" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="20" t="n"/>
-      <c r="G43" s="21" t="n"/>
+      <c r="F43" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>19586</v>
+      </c>
       <c r="H43" s="21" t="n">
         <v>10957</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>37903</v>
+        <v>18317</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>0.7756999999999999</v>
-      </c>
-      <c r="K43" s="25" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="K43" s="29" t="n">
         <v>4.46</v>
       </c>
       <c r="L43" s="23" t="n">
@@ -29653,16 +29736,20 @@
       <c r="E44" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="10" t="n"/>
+      <c r="F44" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>27980</v>
+      </c>
       <c r="H44" s="10" t="n">
         <v>12740</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>57060</v>
+        <v>29080</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.8175</v>
+        <v>0.4166</v>
       </c>
       <c r="K44" s="25" t="n">
         <v>5.48</v>
